--- a/docs/invoices/2026-08/07-079_ファイアープレイス.xlsx
+++ b/docs/invoices/2026-08/07-079_ファイアープレイス.xlsx
@@ -10,7 +10,7 @@
     <sheet name="請求書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>イベント参加日当　7/25　計2名日</t>
+          <t>ファシリテーター稼働費　7/25　12:00〜16:30　4.5時間 × 2名 ＝ 9時間　時給5,000円</t>
         </is>
       </c>
       <c r="B21" s="19" t="n"/>
@@ -903,14 +903,14 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>18182</v>
+        <v>40909</v>
       </c>
       <c r="F21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>交通費　往復実費</t>
+          <t>イベント参加日当　7/25　計2名日</t>
         </is>
       </c>
       <c r="B22" s="19" t="n"/>
@@ -921,16 +921,26 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1218</v>
+        <v>18182</v>
       </c>
       <c r="F22" s="19" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n"/>
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>交通費　往復実費</t>
+        </is>
+      </c>
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="19" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>7月分</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>1218</v>
+      </c>
       <c r="F23" s="19" t="n"/>
     </row>
     <row r="24">
@@ -1093,26 +1103,33 @@
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="35" t="inlineStr">
         <is>
+          <t>・契約期間の開始が2026年7月25日のため、7月は月額報酬の対象外です。7/25の稼働は同別紙の時給5,000円（税込）で算定しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
           <t>・イベント参加日当は1名1日あたり10,000円（税込）、交通費は同別紙の交通費規定（往復上限3,000円・在来線／バス等）に基づく往復実費です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="35" t="inlineStr">
-        <is>
-          <t>・上記の日当・交通費は税込金額で表示しており、明細欄には税抜換算額を記載しています。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="35" t="inlineStr">
         <is>
+          <t>・上記の稼働費・日当・交通費は税込金額で表示しており、明細欄には税抜換算額を記載しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
           <t>・恐れ入りますが振込手数料は貴社にてご負担をお願いいたします。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="C30:D30"/>
@@ -1140,6 +1157,7 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="E30:F30"/>

--- a/docs/invoices/2026-08/07-079_ファイアープレイス.xlsx
+++ b/docs/invoices/2026-08/07-079_ファイアープレイス.xlsx
@@ -838,36 +838,36 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>OSAKA共創LAB　ファシリテーター業務委託費</t>
+          <t>ファシリテーター稼働費　7/25　12:00〜16:30　4.5時間 × 2名 ＝ 9時間　時給5,000円</t>
         </is>
       </c>
       <c r="B18" s="19" t="n"/>
       <c r="C18" s="19" t="n"/>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>8月分</t>
+          <t>7月分</t>
         </is>
       </c>
       <c r="E18" s="21" t="n">
-        <v>272727</v>
+        <v>40909</v>
       </c>
       <c r="F18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>イベント参加日当　8/4・8/18・8/30　計5名日</t>
+          <t>イベント参加日当　7/25　計2名日</t>
         </is>
       </c>
       <c r="B19" s="19" t="n"/>
       <c r="C19" s="19" t="n"/>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>8月分</t>
+          <t>7月分</t>
         </is>
       </c>
       <c r="E19" s="21" t="n">
-        <v>45455</v>
+        <v>18182</v>
       </c>
       <c r="F19" s="19" t="n"/>
     </row>
@@ -881,47 +881,47 @@
       <c r="C20" s="19" t="n"/>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>8月分</t>
+          <t>7月分</t>
         </is>
       </c>
       <c r="E20" s="21" t="n">
-        <v>2600</v>
+        <v>1218</v>
       </c>
       <c r="F20" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>ファシリテーター稼働費　7/25　12:00〜16:30　4.5時間 × 2名 ＝ 9時間　時給5,000円</t>
+          <t>OSAKA共創LAB　ファシリテーター業務委託費</t>
         </is>
       </c>
       <c r="B21" s="19" t="n"/>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>7月分</t>
+          <t>8月分</t>
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>40909</v>
+        <v>272727</v>
       </c>
       <c r="F21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>イベント参加日当　7/25　計2名日</t>
+          <t>イベント参加日当　8/4・8/18・8/30　計5名日</t>
         </is>
       </c>
       <c r="B22" s="19" t="n"/>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>7月分</t>
+          <t>8月分</t>
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>18182</v>
+        <v>45455</v>
       </c>
       <c r="F22" s="19" t="n"/>
     </row>
@@ -935,11 +935,11 @@
       <c r="C23" s="19" t="n"/>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>7月分</t>
+          <t>8月分</t>
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>1218</v>
+        <v>2600</v>
       </c>
       <c r="F23" s="19" t="n"/>
     </row>
